--- a/Verificacion_citas_Cap_III.xlsx
+++ b/Verificacion_citas_Cap_III.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>133</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -638,7 +638,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>(1) SUP-JIN-194/2025: el proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto) y las pp. 43-50 del voto están en el tramo del PDF «compressed-1-300» (7.7 MB), cuya descarga agota la sesión de Drive; el texto que extrae Drive llega sólo a la p. 42 del voto. Quedan 39 notas pendientes por esta causa. (2) Ryle, The Concept of Mind: el ejemplar del Drive es un escaneo de la edición de 1949 sin capa de texto (16.8 MB); la tesis cita la edición de Penguin (1963, reimpr. 1968). Quedan 3 notas pendientes. (3) En el voto de Rodríguez Mondragón las hojas numeradas 21 y 20 (y 11 y 10, 31 y 30, 41 y 40) aparecen en orden inverso; se siguió el número impreso de cada hoja, con el que coinciden las demás citas de la tesis.</t>
+          <t>(1) SUP-JIN-194/2025: el voto de Rodríguez Mondragón y su proyecto se cotejaron con el PDF en tramos (40-120, 121-200 y 200-300) que el usuario puso a disposición. En ese documento varias hojas tienen el número impreso fuera de orden (21 antes que 20, 91 antes que 90, 101 antes que 100, etc.); se siguió el número impreso de cada hoja, que es el que usa la tesis. (2) Ryle, The Concept of Mind: se recibieron las pp. 13-18; la nota 554 (p. 19) queda pendiente.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), p. 1, nota 1: fundamento en el art. 254, último párrafo, LOPJF. La extensión de 51 páginas de la primera parte no pudo verificarse: el texto disponible del voto llega a la p. 42.</t>
+          <t>Voto de Rodríguez Mondragón (PDF subido), p. 1, nota 1 (art. 254 LOPJF); el disenso ocupa las pp. 1-51 y el proyecto se reproduce desde la p. 52.</t>
         </is>
       </c>
       <c r="J63" s="7" t="n"/>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), p. 50 del voto: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
+          <t>Voto de Rodríguez Mondragón (PDF subido), p. 50: «reproduzco íntegramente las consideraciones del proyecto».</t>
         </is>
       </c>
       <c r="J66" s="7" t="n"/>
@@ -3771,17 +3771,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), pp. 89-111: apartado sobre los estándares probatorios (párrs. 79-156).</t>
         </is>
       </c>
       <c r="J67" s="7" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -3863,17 +3863,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párrs. 513-527, pp. 249-252: se acreditan la causal de financiamiento y la violación de principios; no la intervención de partidos ni de servidores públicos.</t>
         </is>
       </c>
       <c r="J69" s="7" t="n"/>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 96, p. 92: plenamente acreditadas significa superar «sin excepción el estándar de prueba previamente fijado».</t>
         </is>
       </c>
       <c r="J74" s="7" t="n"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -4285,17 +4285,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 87, p. 91: definición de estándar de prueba.</t>
         </is>
       </c>
       <c r="J78" s="7" t="n"/>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 88, pp. 91 y 90 (la hoja 91 precede físicamente a la 90), y nota 75 (Ferrer, p. 137): tres funciones.</t>
         </is>
       </c>
       <c r="J79" s="7" t="n"/>
@@ -4377,17 +4377,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 91, p. 90.</t>
         </is>
       </c>
       <c r="J80" s="7" t="n"/>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 130-131, p. 102, y nota 82 (Ferrer, Prueba sin convicción, p. 73).</t>
         </is>
       </c>
       <c r="J81" s="7" t="n"/>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 132 y nota 83, p. 102: probabilidad inductiva; «No así la probabilidad subjetiva ni la probabilidad matemática».</t>
         </is>
       </c>
       <c r="J82" s="7" t="n"/>
@@ -4561,17 +4561,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 82, p. 89: dos estándares.</t>
         </is>
       </c>
       <c r="J84" s="7" t="n"/>
@@ -4607,17 +4607,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 83, pp. 89-91: probabilidad prevalente.</t>
         </is>
       </c>
       <c r="J85" s="7" t="n"/>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 110, p. 96.</t>
         </is>
       </c>
       <c r="J86" s="7" t="n"/>
@@ -4699,17 +4699,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 107-113, pp. 96-97.</t>
         </is>
       </c>
       <c r="J87" s="7" t="n"/>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 114, p. 97: estándar más elevado, próximo a la presunción de inocencia.</t>
         </is>
       </c>
       <c r="J89" s="7" t="n"/>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 115-118, pp. 97-98.</t>
         </is>
       </c>
       <c r="J90" s="7" t="n"/>
@@ -4883,17 +4883,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 119-123, pp. 99 y 101 (la hoja 101 precede físicamente a la 100).</t>
         </is>
       </c>
       <c r="J91" s="7" t="n"/>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 124, p. 101.</t>
         </is>
       </c>
       <c r="J92" s="7" t="n"/>
@@ -5021,17 +5021,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párrs. 304 (p. 174: sólo «indicios fuertes») y 521-527 (pp. 250-252).</t>
         </is>
       </c>
       <c r="J94" s="7" t="n"/>
@@ -5067,17 +5067,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párrs. 317 (p. 181: vista al INE) y 525 (p. 252: posibles actuaciones individuales sin respaldo institucional).</t>
         </is>
       </c>
       <c r="J95" s="7" t="n"/>
@@ -5113,17 +5113,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 119, p. 99: «de manera convincente y con alto grado de certeza».</t>
         </is>
       </c>
       <c r="J96" s="7" t="n"/>
@@ -5159,17 +5159,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 125, p. 101: «de manera inexorable».</t>
         </is>
       </c>
       <c r="J97" s="7" t="n"/>
@@ -5251,17 +5251,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 93-94, pp. 90 y 92.</t>
         </is>
       </c>
       <c r="J99" s="7" t="n"/>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -5343,17 +5343,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 95, p. 92: decisión no particularista ni libérrima; político-moral.</t>
         </is>
       </c>
       <c r="J101" s="7" t="n"/>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 97, pp. 92-93.</t>
         </is>
       </c>
       <c r="J102" s="7" t="n"/>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 97, nota 76, p. 93: cita el caso Tabasco.</t>
         </is>
       </c>
       <c r="J104" s="7" t="n"/>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 99, p. 93: «grado de convencimiento necesario».</t>
         </is>
       </c>
       <c r="J106" s="7" t="n"/>
@@ -5619,17 +5619,17 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 127, pp. 101 y 100.</t>
         </is>
       </c>
       <c r="J107" s="7" t="n"/>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -5761,17 +5761,17 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 139 y nota 85 (SUP-JRC-221/2003), p. 104.</t>
         </is>
       </c>
       <c r="J110" s="7" t="n"/>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), pp. 44-45: fuera del tramo disponible (el texto extraído llega a la p. 42). La correlación del 92.4% sí consta en la p. 38.</t>
+          <t>Voto de Rodríguez Mondragón (PDF subido), pp. 44-45: correlación de 92.4%, índice Herfindahl-Hirschman y Pearson de 0.924.</t>
         </is>
       </c>
       <c r="J119" s="7" t="n"/>
@@ -6229,17 +6229,17 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 86 (p. 91) y 152 (p. 109): la estadística como herramienta adicional.</t>
         </is>
       </c>
       <c r="J120" s="7" t="n"/>
@@ -6275,17 +6275,17 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párrs. 155-156, pp. 109 y 111: secreto del voto.</t>
         </is>
       </c>
       <c r="J121" s="7" t="n"/>
@@ -6321,17 +6321,17 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párr. 321, p. 183: «desmedido exigir… de manera fehaciente la trascendencia… casi imposible de alcanzar»; nota 142 (SUP-REC-2214/2021).</t>
         </is>
       </c>
       <c r="J122" s="7" t="n"/>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 83, pp. 89-91.</t>
         </is>
       </c>
       <c r="J124" s="7" t="n"/>
@@ -6459,17 +6459,17 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H125" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párrs. 471-472, pp. 237-238: «posible causalidad directa»; «imposible descartar la influencia de las guías».</t>
         </is>
       </c>
       <c r="J125" s="7" t="n"/>
@@ -6505,17 +6505,17 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párr. 472, p. 237: «sin la influencia de los acordeones, los resultados electorales no se podrían explicar».</t>
         </is>
       </c>
       <c r="J126" s="7" t="n"/>
@@ -6597,17 +6597,17 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Voto de R. Rodríguez Mondragón, en SUP-JIN-194-2025… compressed-1-300 (texto extraído por Drive; paginación al pie)</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Voto de R. Rodríguez Mondragón (PDF por tramos y texto extraído por Drive)</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), p. 45 del voto: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
+          <t>Voto de Rodríguez Mondragón (PDF subido), p. 45: análisis «de corte transversal».</t>
         </is>
       </c>
       <c r="J128" s="7" t="n"/>
@@ -6643,17 +6643,17 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H129" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párr. 321, pp. 180-183: parámetro del 5%, determinancia cuantitativa y cualitativa.</t>
         </is>
       </c>
       <c r="J129" s="7" t="n"/>
@@ -7057,17 +7057,17 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>SUP-JIN-194/2025, párrs. 39 y 109, pp. 8 y 24: conformes (estándar flexible pedido por la actora; «medios de convicción irrefutables»). Queda pendiente la parte relativa al proyecto de Rodríguez Mondragón, párr. 83, pp. 89-91.</t>
+          <t>SUP-JIN-194/2025, párrs. 39 y 109, pp. 8 y 24; proyecto, párr. 83, pp. 89-91.</t>
         </is>
       </c>
       <c r="J138" s="7" t="n"/>
@@ -9089,17 +9089,17 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 96, p. 92.</t>
         </is>
       </c>
       <c r="J182" s="7" t="n"/>
@@ -9135,17 +9135,17 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>The Concept of Mind (escaneo de 1949 sin capa de texto)</t>
-        </is>
-      </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>The Concept of Mind (pp. 13-18 subidas por el usuario)</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Ryle, The Concept of Mind, p. 17: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
+          <t>Ryle, The Concept of Mind (PDF subido; pp. 13-18 de la edición cuya paginación coincide con la citada), p. 17: «a category-mistake. It represents the facts of mental life as if they belonged to one logical type or category…».</t>
         </is>
       </c>
       <c r="J183" s="7" t="n"/>
@@ -9181,17 +9181,17 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>The Concept of Mind (escaneo de 1949 sin capa de texto)</t>
-        </is>
-      </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>The Concept of Mind (pp. 13-18 subidas por el usuario)</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Ryle, The Concept of Mind, pp. 17-18: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
+          <t>Ryle, pp. 17-18: el visitante de Oxford que pregunta «But where is the University?».</t>
         </is>
       </c>
       <c r="J184" s="7" t="n"/>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>The Concept of Mind (escaneo de 1949 sin capa de texto)</t>
+          <t>The Concept of Mind (pp. 13-18 subidas por el usuario)</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Ryle, The Concept of Mind, p. 19: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
+          <t>Ryle, p. 19: el archivo subido abarca las pp. 13-18; la p. 18 termina con el ejemplo del críquet y el pasaje citado debe seguir en la p. 19, que no se recibió.</t>
         </is>
       </c>
       <c r="J185" s="7" t="n"/>
@@ -9304,7 +9304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9593,7 +9593,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>435</v>
+        <v>554</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
@@ -9602,1040 +9602,15 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Ibidem, p. 50.</t>
+          <t>Ibidem, p. 19.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), p. 50 del voto: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
+          <t>Ryle, p. 19: el archivo subido abarca las pp. 13-18; la p. 18 termina con el ejemplo del críquet y el pasaje citado debe seguir en la p. 19, que no se recibió.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>436</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de sentencia presentado por el magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, reproducido en su voto particular, pp. 89-111 del voto.</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>438</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafos 513 a 527, pp. 249-252.</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>443</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 96, p. 92.</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>447</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 87, p. 91.</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>448</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 88, pp. 90 y 91, y nota 75, donde cita a Ferrer Beltrán, Prueba sin convicción, cit., p. 137.</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>449</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 91, p. 90.</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 130 y 131, p. 102, y nota 82, donde cita a Ferrer Beltrán, Prueba sin convicción, cit., p. 73.</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>451</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 132 y nota 83, p. 102.</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>453</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 82, p. 89.</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>454</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 83, pp. 89-91.</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>455</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 110, p. 96.</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>456</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 107 a 113, pp. 96 y 97.</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>458</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 114, p. 97.</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>459</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 115 a 118, pp. 97 y 98.</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>460</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 119 a 123, pp. 99 y 101.</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>461</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 124, p. 101.</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>463</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafos 304 y 521 a 527, pp. 174 y 250-252.</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>464</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 317 y 525, pp. 181 y 252.</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>465</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 119, p. 99.</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>466</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 125, p. 101.</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>468</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafos 93 y 94, pp. 90 y 92.</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>470</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 95, p. 92.</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>471</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 97, pp. 92 y 93.</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>473</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 97, nota 76, p. 93.</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>475</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 99, p. 93.</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>476</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 127, pp. 100 y 101.</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>479</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 139 y nota 85, p. 104.</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>488</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, pp. 44 y 45.</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), pp. 44-45: fuera del tramo disponible (el texto extraído llega a la p. 42). La correlación del 92.4% sí consta en la p. 38.</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>489</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafos 86 y 152, pp. 91 y 109.</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>490</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 155 y 156, pp. 109 y 111.</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>491</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 321, p. 183, y nota 142, que remite al SUP-REC-2214/2021.</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>493</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 83, pp. 89-91.</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>494</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafos 471 y 472, pp. 237 y 238.</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>495</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 472, p. 237.</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>497</v>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Voto de Rodríguez Mondragón, cit., p. 45.</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Voto particular de Rodríguez Mondragón (SUP-JIN-194/2025), p. 45 del voto: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>498</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 321, pp. 180-183.</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>507</v>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>SUP-JIN-194/2025, cit., párrafos 39 y 109, pp. 8 y 24, y proyecto de Rodríguez Mondragón, cit., párrafo 83, pp. 89-91.</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>SUP-JIN-194/2025, párrs. 39 y 109, pp. 8 y 24: conformes (estándar flexible pedido por la actora; «medios de convicción irrefutables»). Queda pendiente la parte relativa al proyecto de Rodríguez Mondragón, párr. 83, pp. 89-91.</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>551</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de sentencia presentado por el magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, reproducido en su voto particular, párrafo 96, p. 92 del voto.</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (pp. 89-252 del voto): tramo del PDF (págs. 81-300 del archivo «compressed-1-300», 7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>552</v>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Ryle, Gilbert, The Concept of Mind, Harmondsworth, Penguin Books, 1963, reimpresión de 1968, p. 17. La primera edición fue publicada por Hutchinson en 1949.</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Ryle, The Concept of Mind, p. 17: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>553</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, pp. 17 y 18.</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Ryle, The Concept of Mind, pp. 17-18: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>554</v>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, p. 19.</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Ryle, The Concept of Mind, p. 19: el ejemplar del Drive (16.8 MB, edición de 1949 según su título) es un escaneo sin capa de texto y excede el límite de descarga; además, la tesis cita la edición de Penguin (1963, reimpr. 1968), cuya paginación puede diferir de la de 1949.</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Ninguna; requiere la fuente</t>
         </is>
@@ -10757,7 +9732,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Escaneo de 1949 sin capa de texto (16.8 MB)</t>
+          <t>Pp. 13-18 subidas por el usuario (su paginación coincide con la que cita la tesis)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -10767,7 +9742,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>No verificable; la paginación de Penguin puede diferir de la de 1949.</t>
+          <t>Notas 552 y 553 conformes; 554 (p. 19) pendiente.</t>
         </is>
       </c>
     </row>
@@ -10956,7 +9931,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>El proyecto (tramo del PDF de 7.7 MB) no pudo descargarse: 42 notas pendientes.</t>
+          <t>Se verificó con el PDF en tramos; todas las notas conformes o corregidas.</t>
         </is>
       </c>
     </row>
@@ -11136,7 +10111,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Pendiente (fuente no disponible).</t>
+          <t>Conforme.</t>
         </is>
       </c>
     </row>
@@ -11158,7 +10133,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Conforme en lo verificable (voto pp. 17-21 y 38-42); pendiente voto pp. 43-45 y proyecto.</t>
+          <t>Conforme.</t>
         </is>
       </c>
     </row>
@@ -11180,7 +10155,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Conforme en lo verificable; pendiente voto pp. 43-45 y proyecto.</t>
+          <t>Conforme.</t>
         </is>
       </c>
     </row>

--- a/Verificacion_citas_Cap_III.xlsx
+++ b/Verificacion_citas_Cap_III.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -638,7 +638,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>(1) SUP-JIN-194/2025: el voto de Rodríguez Mondragón y su proyecto se cotejaron con el PDF en tramos (40-120, 121-200 y 200-300) que el usuario puso a disposición. En ese documento varias hojas tienen el número impreso fuera de orden (21 antes que 20, 91 antes que 90, 101 antes que 100, etc.); se siguió el número impreso de cada hoja, que es el que usa la tesis. (2) Ryle, The Concept of Mind: se recibieron las pp. 13-18; la nota 554 (p. 19) queda pendiente.</t>
+          <t>SUP-JIN-194/2025: el voto de Rodríguez Mondragón y su proyecto se cotejaron con el PDF en tramos (40-120, 121-200 y 200-300). En ese documento varias hojas tienen el número impreso fuera de orden (21 antes que 20, 91 antes que 90, 101 antes que 100, etc.); se siguió el número impreso de cada hoja, que es el que usa la tesis. Ryle se cotejó con las pp. 13-19 enviadas por el usuario.</t>
         </is>
       </c>
     </row>
@@ -9230,14 +9230,14 @@
           <t>The Concept of Mind (pp. 13-18 subidas por el usuario)</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Ryle, p. 19: el archivo subido abarca las pp. 13-18; la p. 18 termina con el ejemplo del críquet y el pasaje citado debe seguir en la p. 19, que no se recibió.</t>
+          <t>Ryle, The Concept of Mind, p. 19 (imagen enviada por el usuario): «The theoretically interesting category-mistakes are those made by people who are perfectly competent to apply concepts, at least in the situations with which they are familiar, but are still liable in their abstract thinking to allocate those concepts to logical types to which they do not belong».</t>
         </is>
       </c>
       <c r="J185" s="7" t="n"/>
@@ -9304,7 +9304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9588,31 +9588,6 @@
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Nota: «p. 27» → «pp. 27 y 28».</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>554</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, p. 19.</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Ryle, p. 19: el archivo subido abarca las pp. 13-18; la p. 18 termina con el ejemplo del críquet y el pasaje citado debe seguir en la p. 19, que no se recibió.</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9707,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pp. 13-18 subidas por el usuario (su paginación coincide con la que cita la tesis)</t>
+          <t>Pp. 13-19 enviadas por el usuario (su paginación coincide con la que cita la tesis)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9742,7 +9717,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Notas 552 y 553 conformes; 554 (p. 19) pendiente.</t>
+          <t>Notas 552 a 554 conformes.</t>
         </is>
       </c>
     </row>
